--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>137275243</v>
       </c>
       <c r="B3" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137275245</v>
       </c>
       <c r="B4" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>137275243</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137275245</v>
       </c>
       <c r="B4" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>137275243</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137275245</v>
       </c>
       <c r="B4" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20535-2026 artfynd.xlsx
+++ b/artfynd/A 20535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137275236</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>137275243</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>137275245</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
